--- a/output.xlsx
+++ b/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\-=ФОРМИРОВАНИЕ КП=-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8073845-C058-4E15-BE9B-78F456A1CCE0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDFDE1F-2B2E-49B4-9FE6-7368D16B3853}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1381">
   <si>
     <t>Номер п/п</t>
   </si>
@@ -2124,9 +2124,6 @@
     <t>Спецодежда</t>
   </si>
   <si>
-    <t>2151132@klinpark.ru, info@klinpark.ru</t>
-  </si>
-  <si>
     <t>Пиломатериалы</t>
   </si>
   <si>
@@ -3613,9 +3610,6 @@
     <t>Двери</t>
   </si>
   <si>
-    <t>torg.nf@gmail.com, adolvl@mail.ru</t>
-  </si>
-  <si>
     <t>prostoryz@mail.ru</t>
   </si>
   <si>
@@ -3643,9 +3637,6 @@
     <t>Медтовары, подгузники</t>
   </si>
   <si>
-    <t>Лекарства, медтовары, подгузники</t>
-  </si>
-  <si>
     <t xml:space="preserve">ООО "АМЕДИС ИНЖИНИРИНГ" </t>
   </si>
   <si>
@@ -3740,9 +3731,6 @@
   </si>
   <si>
     <t>141216, МОСКОВСКАЯ ОБЛАСТЬ, г.о. ПУШКИНСКИЙ, Г ПУШКИНО, Ш ЯРОСЛАВСКОЕ, Д. 228</t>
-  </si>
-  <si>
-    <t>garant@garant1.ru</t>
   </si>
   <si>
     <t>ООО "БАРИОН"</t>
@@ -4094,6 +4082,121 @@
   </si>
   <si>
     <t>farmbox.torgi@gmail.com</t>
+  </si>
+  <si>
+    <t>Перчатки, шприцы</t>
+  </si>
+  <si>
+    <t>Лекарства, перчатки, подгузники, шприцы</t>
+  </si>
+  <si>
+    <t>Лекарства, шприцы</t>
+  </si>
+  <si>
+    <t>2151132@klinpark.ru, info@klinpark.ru, anisimov@klinpark.ru</t>
+  </si>
+  <si>
+    <t>ЮРЬЕВ ВЛАДИСЛАВ ИГОРЕВИЧ</t>
+  </si>
+  <si>
+    <t>301610485490</t>
+  </si>
+  <si>
+    <t>141700, Московская обл., г. Долгопрудный, б-р
+Космонавта Сереброва А.А., д. 4</t>
+  </si>
+  <si>
+    <t>ipyuriev@bk.ru</t>
+  </si>
+  <si>
+    <t>ООО "ВОЛНА"</t>
+  </si>
+  <si>
+    <t>6230114532</t>
+  </si>
+  <si>
+    <t>volnafarma@yandex.ru</t>
+  </si>
+  <si>
+    <t>390037, РЯЗАНСКАЯ ОБЛАСТЬ, Г. РЯЗАНЬ, УЛ. БОЛЬШАЯ, Д. 94, ПОМЕЩ. Н81</t>
+  </si>
+  <si>
+    <t>ООО "ЛЕГАС-ТРЕЙД"</t>
+  </si>
+  <si>
+    <t>3443142095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400048, Волгоградская область, город Волгоград, Авторемонтная ул., д. 11в, помещ. 3 </t>
+  </si>
+  <si>
+    <t>sukhanov.vladimir@legastrade.ru</t>
+  </si>
+  <si>
+    <t>torg.nf@gmail.com, adolvl@mail.ru, aguta2017@mail.ru</t>
+  </si>
+  <si>
+    <t>ООО "РЕАЛМЕД"</t>
+  </si>
+  <si>
+    <t>5259108307</t>
+  </si>
+  <si>
+    <t>realmed-nn@yandex.ru</t>
+  </si>
+  <si>
+    <t>603076, НИЖЕГОРОДСКАЯ ОБЛАСТЬ, Г. НИЖНИЙ НОВГОРОД, ПР-КТ ЛЕНИНА, Д. 48Д, КВ. 146</t>
+  </si>
+  <si>
+    <t>garant@garant1.ru torgietp@yandex.ru</t>
+  </si>
+  <si>
+    <t>ВАХРУШЕВА НАТАЛЬЯ ВЛАДИМИРОВНА</t>
+  </si>
+  <si>
+    <t>667108520620</t>
+  </si>
+  <si>
+    <t>620130, СВЕРДЛОВСКАЯ ОБЛАСТЬ, г.о. ГОРОД ЕКАТЕРИНБУРГ, Г ЕКАТЕРИНБУРГ, УЛ ЮЛИУСА ФУЧИКА, Д. 5, КВ. 32</t>
+  </si>
+  <si>
+    <t>info@ipvah.ru</t>
+  </si>
+  <si>
+    <t>ООО "УНИКСМЕД"</t>
+  </si>
+  <si>
+    <t>6700028620</t>
+  </si>
+  <si>
+    <t>214013, СМОЛЕНСКАЯ ОБЛАСТЬ, г.о. ГОРОД СМОЛЕНСК, Г СМОЛЕНСК, УЛ НИКОЛАЕВА, Д. 51, ОФИС М 3</t>
+  </si>
+  <si>
+    <t>unixmed2025@gmail.com mila1410_14@mail.ru</t>
+  </si>
+  <si>
+    <t>ООО "СПЕЦИАЛ-ИНВЕСТ"</t>
+  </si>
+  <si>
+    <t>9728047498</t>
+  </si>
+  <si>
+    <t>101000, Г.МОСКВА, вн.тер.г. МУНИЦИПАЛЬНЫЙ ОКРУГ КРАСНОСЕЛЬСКИЙ, ПЕР УЛАНСКИЙ, Д. 22, СТР. 1, ПОМЕЩ. 1Н/6</t>
+  </si>
+  <si>
+    <t>specinvest1@yandex.ru</t>
+  </si>
+  <si>
+    <t>НИКОНЕНКО ЕЛЕНА ЛЕОНИДОВНА</t>
+  </si>
+  <si>
+    <t>742002041233</t>
+  </si>
+  <si>
+    <t>456440, ЧЕЛЯБИНСКАЯ ОБЛАСТЬ, Г. ЧЕБАРКУЛЬ, УЛ. 8 МАРТА, Д. 7, КВ. 106</t>
+  </si>
+  <si>
+    <t>darja_kolos@mail.ru</t>
   </si>
 </sst>
 </file>
@@ -4496,7 +4599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G456"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.140625" customWidth="1"/>
@@ -4524,7 +4627,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -4586,16 +4689,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C5" s="3">
         <v>5261037364</v>
       </c>
       <c r="D5" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="F5" t="s">
         <v>654</v>
@@ -4606,7 +4709,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C6" s="3">
         <v>7714461708</v>
@@ -4640,7 +4743,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C8" s="3">
         <v>5256190656</v>
@@ -4657,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C9" s="3">
         <v>5262212308</v>
@@ -4722,7 +4825,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C13" s="3">
         <v>5257123081</v>
@@ -4739,7 +4842,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C14" s="3">
         <v>5256056266</v>
@@ -4782,7 +4885,7 @@
         <v>5262383871</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="F16" t="s">
         <v>654</v>
@@ -4793,7 +4896,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C17" s="3">
         <v>5260055963</v>
@@ -4861,7 +4964,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C21" s="3">
         <v>5257188868</v>
@@ -4875,7 +4978,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C22" s="3">
         <v>5256139427</v>
@@ -4926,7 +5029,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C25" s="3">
         <v>5256063986</v>
@@ -5011,7 +5114,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>653</v>
@@ -5037,7 +5140,7 @@
         <v>358</v>
       </c>
       <c r="F31" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,10 +5165,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>125</v>
@@ -5113,7 +5216,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C36" s="3">
         <v>5262330414</v>
@@ -5147,10 +5250,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D38" t="s">
         <v>481</v>
@@ -5272,7 +5375,7 @@
         <v>458</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>459</v>
@@ -5286,7 +5389,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C46" s="3">
         <v>5258000780</v>
@@ -5303,10 +5406,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>67</v>
@@ -5320,7 +5423,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C48" s="3">
         <v>1215027621</v>
@@ -5354,10 +5457,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D50" t="s">
         <v>500</v>
@@ -5380,7 +5483,7 @@
         <v>5262334916</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F51" t="s">
         <v>670</v>
@@ -5394,7 +5497,7 @@
         <v>388</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>389</v>
@@ -5408,19 +5511,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D53" t="s">
         <v>527</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="F53" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5428,19 +5531,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D54" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F54" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -5448,19 +5551,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>1147</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="E55" s="7" t="s">
         <v>1149</v>
       </c>
-      <c r="D55" s="4" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>1150</v>
-      </c>
       <c r="F55" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -5468,16 +5571,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D56" t="s">
         <v>98</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="F56" t="s">
         <v>676</v>
@@ -5488,7 +5591,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C57" s="3">
         <v>7714900049</v>
@@ -5505,7 +5608,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C58" s="3">
         <v>7726416643</v>
@@ -5522,7 +5625,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C59" s="3">
         <v>5260316453</v>
@@ -5539,7 +5642,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C60" s="3">
         <v>5261038946</v>
@@ -5556,7 +5659,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>641</v>
@@ -5582,10 +5685,10 @@
         <v>132</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F62" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5596,13 +5699,13 @@
         <v>330</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>331</v>
       </c>
       <c r="F63" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5630,7 +5733,7 @@
         <v>91</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>92</v>
@@ -5647,10 +5750,10 @@
         <v>120</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="F66" t="s">
         <v>668</v>
@@ -5678,10 +5781,10 @@
         <v>68</v>
       </c>
       <c r="B68" t="s">
+        <v>817</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>818</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>819</v>
       </c>
       <c r="D68" t="s">
         <v>473</v>
@@ -5690,7 +5793,7 @@
         <v>474</v>
       </c>
       <c r="F68" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5698,7 +5801,7 @@
         <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C69" s="3">
         <v>7724804707</v>
@@ -5710,7 +5813,7 @@
         <v>484</v>
       </c>
       <c r="F69" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5727,7 +5830,7 @@
         <v>267</v>
       </c>
       <c r="F70" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5738,7 +5841,7 @@
         <v>47</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>48</v>
@@ -5758,10 +5861,10 @@
         <v>665</v>
       </c>
       <c r="D72" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="F72" t="s">
         <v>658</v>
@@ -5772,13 +5875,13 @@
         <v>73</v>
       </c>
       <c r="B73" t="s">
+        <v>850</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>852</v>
-      </c>
       <c r="E73" s="7" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F73" t="s">
         <v>658</v>
@@ -5789,7 +5892,7 @@
         <v>74</v>
       </c>
       <c r="B74" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C74" s="3">
         <v>5260136299</v>
@@ -5798,7 +5901,7 @@
         <v>60</v>
       </c>
       <c r="F74" t="s">
-        <v>658</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5820,10 +5923,10 @@
         <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D76" t="s">
         <v>475</v>
@@ -5857,10 +5960,10 @@
         <v>78</v>
       </c>
       <c r="B78" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D78" t="s">
         <v>485</v>
@@ -5877,10 +5980,10 @@
         <v>79</v>
       </c>
       <c r="B79" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D79" t="s">
         <v>502</v>
@@ -5900,13 +6003,13 @@
         <v>256</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D80" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E80" s="4" t="s">
         <v>1181</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>1182</v>
       </c>
       <c r="F80" t="s">
         <v>658</v>
@@ -5917,10 +6020,10 @@
         <v>81</v>
       </c>
       <c r="B81" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D81" t="s">
         <v>504</v>
@@ -5937,10 +6040,10 @@
         <v>82</v>
       </c>
       <c r="B82" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>506</v>
@@ -5954,10 +6057,10 @@
         <v>83</v>
       </c>
       <c r="B83" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D83" t="s">
         <v>510</v>
@@ -5991,10 +6094,10 @@
         <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>534</v>
@@ -6011,7 +6114,7 @@
         <v>418</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D86" t="s">
         <v>419</v>
@@ -6031,7 +6134,7 @@
         <v>429</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>430</v>
@@ -6045,10 +6148,10 @@
         <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>52</v>
@@ -6057,7 +6160,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>89</v>
       </c>
@@ -6068,10 +6171,10 @@
         <v>7728658430</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>1188</v>
+        <v>1359</v>
       </c>
       <c r="F89" t="s">
-        <v>1198</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -6079,13 +6182,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="F90" t="s">
         <v>658</v>
@@ -6096,16 +6199,16 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>535</v>
       </c>
       <c r="F91" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -6122,7 +6225,7 @@
         <v>263</v>
       </c>
       <c r="F92" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -6130,7 +6233,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C93" s="3">
         <v>4345435031</v>
@@ -6142,7 +6245,7 @@
         <v>531</v>
       </c>
       <c r="F93" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -6150,7 +6253,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C94" s="3">
         <v>5254019526</v>
@@ -6170,7 +6273,7 @@
         <v>425</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>426</v>
@@ -6193,7 +6296,7 @@
         <v>97</v>
       </c>
       <c r="F96" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -6218,10 +6321,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>509</v>
@@ -6235,13 +6338,13 @@
         <v>100</v>
       </c>
       <c r="B99" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="E99" s="7" t="s">
         <v>1018</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>1019</v>
       </c>
       <c r="F99" t="s">
         <v>687</v>
@@ -6252,7 +6355,7 @@
         <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>592</v>
@@ -6272,7 +6375,7 @@
         <v>113</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>114</v>
@@ -6286,7 +6389,7 @@
         <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C102" s="3">
         <v>7839423761</v>
@@ -6337,7 +6440,7 @@
         <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C105" s="3">
         <v>5257186349</v>
@@ -6354,7 +6457,7 @@
         <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C106" s="3">
         <v>7733295245</v>
@@ -6363,7 +6466,7 @@
         <v>189</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="F106" t="s">
         <v>657</v>
@@ -6374,7 +6477,7 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C107" s="3">
         <v>5050040390</v>
@@ -6394,7 +6497,7 @@
         <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C108" s="3">
         <v>7728727482</v>
@@ -6414,7 +6517,7 @@
         <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C109" s="3">
         <v>9721058557</v>
@@ -6434,7 +6537,7 @@
         <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C110" s="3">
         <v>5258140033</v>
@@ -6457,7 +6560,7 @@
         <v>6316204139</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F111" t="s">
         <v>657</v>
@@ -6477,7 +6580,7 @@
         <v>315</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="F112" t="s">
         <v>657</v>
@@ -6488,13 +6591,13 @@
         <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C113" s="3">
         <v>7706808138</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="F113" t="s">
         <v>657</v>
@@ -6505,13 +6608,13 @@
         <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C114" s="3">
         <v>7751520197</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="F114" t="s">
         <v>657</v>
@@ -6522,7 +6625,7 @@
         <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>656</v>
@@ -6531,7 +6634,7 @@
         <v>550</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="F115" t="s">
         <v>657</v>
@@ -6542,16 +6645,16 @@
         <v>117</v>
       </c>
       <c r="B116" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>1135</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="D116" s="4" t="s">
         <v>1136</v>
       </c>
-      <c r="D116" s="4" t="s">
+      <c r="E116" s="7" t="s">
         <v>1137</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>1138</v>
       </c>
       <c r="F116" t="s">
         <v>657</v>
@@ -6562,16 +6665,16 @@
         <v>118</v>
       </c>
       <c r="B117" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E117" s="7" t="s">
         <v>1139</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D117" t="s">
-        <v>1142</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>1140</v>
       </c>
       <c r="F117" t="s">
         <v>657</v>
@@ -6582,7 +6685,7 @@
         <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>666</v>
@@ -6594,7 +6697,7 @@
         <v>56</v>
       </c>
       <c r="F118" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6602,16 +6705,16 @@
         <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>61</v>
       </c>
       <c r="F119" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6619,10 +6722,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>59</v>
@@ -6636,10 +6739,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>66</v>
@@ -6693,10 +6796,10 @@
         <v>5263126355</v>
       </c>
       <c r="D124" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F124" t="s">
         <v>630</v>
@@ -6707,16 +6810,16 @@
         <v>126</v>
       </c>
       <c r="B125" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D125" t="s">
         <v>1021</v>
       </c>
-      <c r="C125" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="E125" s="4" t="s">
         <v>1022</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>1023</v>
       </c>
       <c r="F125" t="s">
         <v>630</v>
@@ -6756,7 +6859,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>129</v>
       </c>
@@ -6767,7 +6870,7 @@
         <v>5257153880</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>693</v>
+        <v>1346</v>
       </c>
       <c r="F128" t="s">
         <v>630</v>
@@ -6778,10 +6881,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>497</v>
@@ -6812,7 +6915,7 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C131" s="3">
         <v>5263088501</v>
@@ -6869,7 +6972,7 @@
         <v>7842413611</v>
       </c>
       <c r="D134" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>337</v>
@@ -6883,16 +6986,16 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" t="s">
         <v>1028</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" s="7" t="s">
         <v>1029</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>1030</v>
       </c>
       <c r="F135" t="s">
         <v>630</v>
@@ -6906,7 +7009,7 @@
         <v>370</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>371</v>
@@ -6940,7 +7043,7 @@
         <v>453</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>590</v>
@@ -6971,16 +7074,16 @@
         <v>141</v>
       </c>
       <c r="B140" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>1127</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" t="s">
         <v>1128</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" s="7" t="s">
         <v>1129</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>1130</v>
       </c>
       <c r="F140" t="s">
         <v>630</v>
@@ -6994,7 +7097,7 @@
         <v>674</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D141" t="s">
         <v>95</v>
@@ -7014,7 +7117,7 @@
         <v>64</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>65</v>
@@ -7028,10 +7131,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>90</v>
@@ -7045,10 +7148,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>541</v>
@@ -7062,7 +7165,7 @@
         <v>146</v>
       </c>
       <c r="B145" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C145" s="3">
         <v>3702161702</v>
@@ -7082,7 +7185,7 @@
         <v>147</v>
       </c>
       <c r="B146" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C146" s="3">
         <v>3702055863</v>
@@ -7116,10 +7219,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>490</v>
@@ -7133,7 +7236,7 @@
         <v>150</v>
       </c>
       <c r="B149" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C149" s="3">
         <v>3702569361</v>
@@ -7170,7 +7273,7 @@
         <v>152</v>
       </c>
       <c r="B151" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C151" s="3">
         <v>3702132892</v>
@@ -7187,7 +7290,7 @@
         <v>153</v>
       </c>
       <c r="B152" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C152" s="3">
         <v>7602126998</v>
@@ -7241,7 +7344,7 @@
         <v>156</v>
       </c>
       <c r="B155" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C155" s="3">
         <v>7702716207</v>
@@ -7298,10 +7401,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="s">
+        <v>719</v>
+      </c>
+      <c r="C158" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>721</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>369</v>
@@ -7315,7 +7418,7 @@
         <v>160</v>
       </c>
       <c r="B159" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C159" s="3">
         <v>7702469886</v>
@@ -7329,13 +7432,13 @@
         <v>161</v>
       </c>
       <c r="B160" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C160" s="3">
         <v>2127325645</v>
       </c>
       <c r="D160" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>395</v>
@@ -7349,10 +7452,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E161" s="4" t="s">
         <v>532</v>
@@ -7366,10 +7469,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D162" t="s">
         <v>402</v>
@@ -7423,10 +7526,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E165" s="4" t="s">
         <v>547</v>
@@ -7440,10 +7543,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E166" s="4" t="s">
         <v>551</v>
@@ -7457,7 +7560,7 @@
         <v>168</v>
       </c>
       <c r="B167" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C167" s="3">
         <v>3702744800</v>
@@ -7477,7 +7580,7 @@
         <v>169</v>
       </c>
       <c r="B168" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>6</v>
@@ -7497,10 +7600,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E169" s="4" t="s">
         <v>579</v>
@@ -7531,7 +7634,7 @@
         <v>172</v>
       </c>
       <c r="B171" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C171" s="3">
         <v>7801132555</v>
@@ -7543,7 +7646,7 @@
         <v>488</v>
       </c>
       <c r="F171" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7551,7 +7654,7 @@
         <v>173</v>
       </c>
       <c r="B172" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C172" s="3">
         <v>7801097614</v>
@@ -7563,7 +7666,7 @@
         <v>499</v>
       </c>
       <c r="F172" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -7574,10 +7677,10 @@
         <v>51</v>
       </c>
       <c r="C173" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="E173" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>772</v>
       </c>
       <c r="F173" t="s">
         <v>678</v>
@@ -7591,7 +7694,7 @@
         <v>78</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E174" s="4" t="s">
         <v>79</v>
@@ -7605,7 +7708,7 @@
         <v>176</v>
       </c>
       <c r="B175" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C175" s="3">
         <v>5260000435</v>
@@ -7659,7 +7762,7 @@
         <v>289</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D178" t="s">
         <v>515</v>
@@ -7693,7 +7796,7 @@
         <v>181</v>
       </c>
       <c r="B180" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C180" s="3">
         <v>5246049622</v>
@@ -7710,10 +7813,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E181" s="4" t="s">
         <v>335</v>
@@ -7747,7 +7850,7 @@
         <v>384</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E183" s="4" t="s">
         <v>385</v>
@@ -7764,7 +7867,7 @@
         <v>400</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E184" s="4" t="s">
         <v>401</v>
@@ -7798,7 +7901,7 @@
         <v>442</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E186" s="4" t="s">
         <v>443</v>
@@ -7829,13 +7932,13 @@
         <v>189</v>
       </c>
       <c r="B188" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C188" s="3" t="s">
         <v>1039</v>
       </c>
-      <c r="C188" s="3" t="s">
+      <c r="E188" s="7" t="s">
         <v>1040</v>
-      </c>
-      <c r="E188" s="7" t="s">
-        <v>1041</v>
       </c>
       <c r="F188" t="s">
         <v>678</v>
@@ -7846,13 +7949,13 @@
         <v>190</v>
       </c>
       <c r="B189" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E189" s="7" t="s">
         <v>1042</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E189" s="7" t="s">
-        <v>1043</v>
       </c>
       <c r="F189" t="s">
         <v>678</v>
@@ -7863,16 +7966,16 @@
         <v>191</v>
       </c>
       <c r="B190" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C190" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="D190" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E190" s="7" t="s">
         <v>1046</v>
-      </c>
-      <c r="D190" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>1047</v>
       </c>
       <c r="F190" t="s">
         <v>678</v>
@@ -7883,16 +7986,16 @@
         <v>192</v>
       </c>
       <c r="B191" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D191" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E191" s="7" t="s">
         <v>1049</v>
-      </c>
-      <c r="C191" s="3" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D191" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E191" s="7" t="s">
-        <v>1050</v>
       </c>
       <c r="F191" t="s">
         <v>678</v>
@@ -7903,16 +8006,16 @@
         <v>193</v>
       </c>
       <c r="B192" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D192" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E192" s="7" t="s">
         <v>1051</v>
-      </c>
-      <c r="C192" s="3" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D192" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E192" s="7" t="s">
-        <v>1052</v>
       </c>
       <c r="F192" t="s">
         <v>678</v>
@@ -7923,16 +8026,16 @@
         <v>194</v>
       </c>
       <c r="B193" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="C193" s="3" t="s">
+      <c r="D193" t="s">
         <v>1058</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" s="7" t="s">
         <v>1059</v>
-      </c>
-      <c r="E193" s="7" t="s">
-        <v>1060</v>
       </c>
       <c r="F193" t="s">
         <v>678</v>
@@ -7943,16 +8046,16 @@
         <v>195</v>
       </c>
       <c r="B194" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D194" t="s">
         <v>1061</v>
       </c>
-      <c r="C194" s="3" t="s">
+      <c r="E194" s="7" t="s">
         <v>1063</v>
-      </c>
-      <c r="D194" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E194" s="7" t="s">
-        <v>1064</v>
       </c>
       <c r="F194" t="s">
         <v>678</v>
@@ -7963,16 +8066,16 @@
         <v>196</v>
       </c>
       <c r="B195" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="D195" t="s">
         <v>1066</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" s="7" t="s">
         <v>1067</v>
-      </c>
-      <c r="E195" s="7" t="s">
-        <v>1068</v>
       </c>
       <c r="F195" t="s">
         <v>678</v>
@@ -7983,16 +8086,16 @@
         <v>197</v>
       </c>
       <c r="B196" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C196" s="3" t="s">
         <v>1069</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="D196" t="s">
         <v>1070</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" s="7" t="s">
         <v>1071</v>
-      </c>
-      <c r="E196" s="7" t="s">
-        <v>1072</v>
       </c>
       <c r="F196" t="s">
         <v>678</v>
@@ -8003,16 +8106,16 @@
         <v>198</v>
       </c>
       <c r="B197" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C197" s="3" t="s">
         <v>1073</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="D197" t="s">
         <v>1074</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" s="7" t="s">
         <v>1075</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>1076</v>
       </c>
       <c r="F197" t="s">
         <v>678</v>
@@ -8023,16 +8126,16 @@
         <v>199</v>
       </c>
       <c r="B198" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C198" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="D198" t="s">
         <v>1078</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" s="7" t="s">
         <v>1079</v>
-      </c>
-      <c r="E198" s="7" t="s">
-        <v>1080</v>
       </c>
       <c r="F198" t="s">
         <v>678</v>
@@ -8043,16 +8146,16 @@
         <v>200</v>
       </c>
       <c r="B199" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C199" s="3" t="s">
         <v>1081</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="D199" t="s">
         <v>1082</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" s="7" t="s">
         <v>1083</v>
-      </c>
-      <c r="E199" s="7" t="s">
-        <v>1084</v>
       </c>
       <c r="F199" t="s">
         <v>678</v>
@@ -8063,16 +8166,16 @@
         <v>201</v>
       </c>
       <c r="B200" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C200" s="3" t="s">
         <v>1085</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="D200" t="s">
         <v>1086</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" s="7" t="s">
         <v>1087</v>
-      </c>
-      <c r="E200" s="7" t="s">
-        <v>1088</v>
       </c>
       <c r="F200" t="s">
         <v>678</v>
@@ -8083,16 +8186,16 @@
         <v>202</v>
       </c>
       <c r="B201" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C201" s="3" t="s">
         <v>1089</v>
       </c>
-      <c r="C201" s="3" t="s">
+      <c r="D201" t="s">
         <v>1090</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" s="7" t="s">
         <v>1091</v>
-      </c>
-      <c r="E201" s="7" t="s">
-        <v>1092</v>
       </c>
       <c r="F201" t="s">
         <v>678</v>
@@ -8103,16 +8206,16 @@
         <v>203</v>
       </c>
       <c r="B202" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C202" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="D202" t="s">
         <v>1094</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" s="7" t="s">
         <v>1095</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>1096</v>
       </c>
       <c r="F202" t="s">
         <v>678</v>
@@ -8123,16 +8226,16 @@
         <v>204</v>
       </c>
       <c r="B203" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C203" s="3" t="s">
         <v>1097</v>
       </c>
-      <c r="C203" s="3" t="s">
+      <c r="D203" t="s">
         <v>1098</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" s="7" t="s">
         <v>1099</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>1100</v>
       </c>
       <c r="F203" t="s">
         <v>678</v>
@@ -8143,16 +8246,16 @@
         <v>205</v>
       </c>
       <c r="B204" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C204" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="D204" t="s">
         <v>1102</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" s="7" t="s">
         <v>1103</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>1104</v>
       </c>
       <c r="F204" t="s">
         <v>678</v>
@@ -8163,16 +8266,16 @@
         <v>206</v>
       </c>
       <c r="B205" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C205" s="3" t="s">
         <v>1105</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="D205" t="s">
         <v>1106</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" s="7" t="s">
         <v>1107</v>
-      </c>
-      <c r="E205" s="7" t="s">
-        <v>1108</v>
       </c>
       <c r="F205" t="s">
         <v>678</v>
@@ -8183,16 +8286,16 @@
         <v>207</v>
       </c>
       <c r="B206" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C206" s="3" t="s">
         <v>1109</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="D206" t="s">
         <v>1110</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" s="7" t="s">
         <v>1111</v>
-      </c>
-      <c r="E206" s="7" t="s">
-        <v>1112</v>
       </c>
       <c r="F206" t="s">
         <v>678</v>
@@ -8203,16 +8306,16 @@
         <v>208</v>
       </c>
       <c r="B207" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C207" s="3" t="s">
         <v>1113</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="D207" t="s">
         <v>1114</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" s="7" t="s">
         <v>1115</v>
-      </c>
-      <c r="E207" s="7" t="s">
-        <v>1116</v>
       </c>
       <c r="F207" t="s">
         <v>678</v>
@@ -8223,16 +8326,16 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D208" t="s">
         <v>1117</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="E208" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="D208" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E208" s="7" t="s">
-        <v>1120</v>
       </c>
       <c r="F208" t="s">
         <v>678</v>
@@ -8246,16 +8349,16 @@
         <v>346</v>
       </c>
       <c r="C209" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D209" t="s">
         <v>810</v>
-      </c>
-      <c r="D209" t="s">
-        <v>811</v>
       </c>
       <c r="E209" s="4" t="s">
         <v>347</v>
       </c>
       <c r="F209" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -8263,7 +8366,7 @@
         <v>212</v>
       </c>
       <c r="B210" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>608</v>
@@ -8280,7 +8383,7 @@
         <v>213</v>
       </c>
       <c r="B211" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>607</v>
@@ -8297,13 +8400,13 @@
         <v>214</v>
       </c>
       <c r="B212" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C212" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="E212" s="7" t="s">
         <v>1037</v>
-      </c>
-      <c r="E212" s="7" t="s">
-        <v>1038</v>
       </c>
       <c r="F212" t="s">
         <v>612</v>
@@ -8317,7 +8420,7 @@
         <v>109</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E213" s="4" t="s">
         <v>110</v>
@@ -8331,7 +8434,7 @@
         <v>216</v>
       </c>
       <c r="B214" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>609</v>
@@ -8348,7 +8451,7 @@
         <v>217</v>
       </c>
       <c r="B215" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C215" s="3">
         <v>5260258508</v>
@@ -8365,10 +8468,10 @@
         <v>218</v>
       </c>
       <c r="B216" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D216" t="s">
         <v>507</v>
@@ -8385,7 +8488,7 @@
         <v>219</v>
       </c>
       <c r="B217" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>610</v>
@@ -8408,7 +8511,7 @@
         <v>435</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E218" s="4" t="s">
         <v>436</v>
@@ -8422,10 +8525,10 @@
         <v>221</v>
       </c>
       <c r="B219" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E219" s="4" t="s">
         <v>457</v>
@@ -8456,7 +8559,7 @@
         <v>223</v>
       </c>
       <c r="B221" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>640</v>
@@ -8465,7 +8568,7 @@
         <v>576</v>
       </c>
       <c r="F221" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8473,16 +8576,16 @@
         <v>224</v>
       </c>
       <c r="B222" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>469</v>
       </c>
       <c r="F222" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8490,16 +8593,16 @@
         <v>225</v>
       </c>
       <c r="B223" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>479</v>
       </c>
       <c r="F223" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8507,19 +8610,19 @@
         <v>226</v>
       </c>
       <c r="B224" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C224" s="3" t="s">
         <v>1152</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="D224" t="s">
         <v>1153</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" s="7" t="s">
         <v>1154</v>
       </c>
-      <c r="E224" s="7" t="s">
-        <v>1155</v>
-      </c>
       <c r="F224" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -8527,19 +8630,19 @@
         <v>227</v>
       </c>
       <c r="B225" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D225" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="C225" s="3" t="s">
-        <v>1156</v>
-      </c>
-      <c r="D225" s="4" t="s">
+      <c r="E225" s="7" t="s">
         <v>1158</v>
       </c>
-      <c r="E225" s="7" t="s">
-        <v>1159</v>
-      </c>
       <c r="F225" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8556,7 +8659,7 @@
         <v>248</v>
       </c>
       <c r="F226" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -8581,10 +8684,10 @@
         <v>230</v>
       </c>
       <c r="B228" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>43</v>
@@ -8615,7 +8718,7 @@
         <v>232</v>
       </c>
       <c r="B230" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>605</v>
@@ -8632,7 +8735,7 @@
         <v>233</v>
       </c>
       <c r="B231" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>602</v>
@@ -8669,7 +8772,7 @@
         <v>235</v>
       </c>
       <c r="B233" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C233" s="3">
         <v>5257140464</v>
@@ -8686,7 +8789,7 @@
         <v>236</v>
       </c>
       <c r="B234" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C234" s="3">
         <v>5261087580</v>
@@ -8723,7 +8826,7 @@
         <v>342</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>343</v>
@@ -8737,10 +8840,10 @@
         <v>239</v>
       </c>
       <c r="B237" t="s">
+        <v>812</v>
+      </c>
+      <c r="C237" s="3" t="s">
         <v>813</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="D237" t="s">
         <v>359</v>
@@ -8757,7 +8860,7 @@
         <v>240</v>
       </c>
       <c r="B238" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C238" s="3">
         <v>5258068806</v>
@@ -8766,7 +8869,7 @@
         <v>524</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F238" t="s">
         <v>629</v>
@@ -8777,7 +8880,7 @@
         <v>241</v>
       </c>
       <c r="B239" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C239" s="3">
         <v>5263094791</v>
@@ -8794,10 +8897,10 @@
         <v>242</v>
       </c>
       <c r="B240" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E240" s="4" t="s">
         <v>414</v>
@@ -8814,7 +8917,7 @@
         <v>415</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>416</v>
@@ -8848,13 +8951,13 @@
         <v>552</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D243" t="s">
         <v>553</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F243" t="s">
         <v>629</v>
@@ -8865,7 +8968,7 @@
         <v>246</v>
       </c>
       <c r="B244" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C244" s="3">
         <v>5250064133</v>
@@ -8902,7 +9005,7 @@
         <v>248</v>
       </c>
       <c r="B246" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>645</v>
@@ -8919,7 +9022,7 @@
         <v>249</v>
       </c>
       <c r="B247" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>649</v>
@@ -8939,7 +9042,7 @@
         <v>250</v>
       </c>
       <c r="B248" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C248" s="3">
         <v>52631010430</v>
@@ -8956,16 +9059,16 @@
         <v>251</v>
       </c>
       <c r="B249" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C249" s="3" t="s">
         <v>1121</v>
       </c>
-      <c r="C249" s="3" t="s">
+      <c r="D249" t="s">
         <v>1122</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" s="7" t="s">
         <v>1123</v>
-      </c>
-      <c r="E249" s="7" t="s">
-        <v>1124</v>
       </c>
       <c r="F249" t="s">
         <v>629</v>
@@ -8985,7 +9088,7 @@
         <v>295</v>
       </c>
       <c r="F250" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8996,13 +9099,13 @@
         <v>669</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>63</v>
       </c>
       <c r="F251" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -9010,16 +9113,16 @@
         <v>254</v>
       </c>
       <c r="B252" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E252" s="4" t="s">
         <v>68</v>
       </c>
       <c r="F252" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -9027,10 +9130,10 @@
         <v>255</v>
       </c>
       <c r="B253" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D253" t="s">
         <v>513</v>
@@ -9039,7 +9142,7 @@
         <v>514</v>
       </c>
       <c r="F253" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -9047,10 +9150,10 @@
         <v>256</v>
       </c>
       <c r="B254" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D254" t="s">
         <v>470</v>
@@ -9059,7 +9162,7 @@
         <v>471</v>
       </c>
       <c r="F254" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -9067,7 +9170,7 @@
         <v>257</v>
       </c>
       <c r="B255" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C255" s="3">
         <v>5260072045</v>
@@ -9084,7 +9187,7 @@
         <v>258</v>
       </c>
       <c r="B256" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C256" s="3">
         <v>5260393666</v>
@@ -9118,7 +9221,7 @@
         <v>260</v>
       </c>
       <c r="B258" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>600</v>
@@ -9172,7 +9275,7 @@
         <v>263</v>
       </c>
       <c r="B261" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>39</v>
@@ -9209,7 +9312,7 @@
         <v>206</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>207</v>
@@ -9226,7 +9329,7 @@
         <v>101</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E264" s="4" t="s">
         <v>102</v>
@@ -9328,7 +9431,7 @@
         <v>272</v>
       </c>
       <c r="B270" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C270" s="3">
         <v>5752028900</v>
@@ -9345,7 +9448,7 @@
         <v>273</v>
       </c>
       <c r="B271" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C271" s="3">
         <v>7720371812</v>
@@ -9362,7 +9465,7 @@
         <v>274</v>
       </c>
       <c r="B272" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C272" s="3">
         <v>5248024214</v>
@@ -9379,10 +9482,10 @@
         <v>275</v>
       </c>
       <c r="B273" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E273" s="4" t="s">
         <v>556</v>
@@ -9396,19 +9499,19 @@
         <v>276</v>
       </c>
       <c r="B274" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C274" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="C274" s="3" t="s">
+      <c r="D274" t="s">
         <v>1032</v>
       </c>
-      <c r="D274" t="s">
+      <c r="E274" s="7" t="s">
         <v>1033</v>
       </c>
-      <c r="E274" s="7" t="s">
+      <c r="F274" t="s">
         <v>1034</v>
-      </c>
-      <c r="F274" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9416,7 +9519,7 @@
         <v>277</v>
       </c>
       <c r="B275" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C275" s="3">
         <v>5256121010</v>
@@ -9487,7 +9590,7 @@
         <v>281</v>
       </c>
       <c r="B279" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>626</v>
@@ -9510,7 +9613,7 @@
         <v>41</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>42</v>
@@ -9527,7 +9630,7 @@
         <v>86</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E281" s="4" t="s">
         <v>87</v>
@@ -9541,10 +9644,10 @@
         <v>284</v>
       </c>
       <c r="B282" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F282" t="s">
         <v>616</v>
@@ -9555,7 +9658,7 @@
         <v>285</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>635</v>
@@ -9572,10 +9675,10 @@
         <v>286</v>
       </c>
       <c r="B284" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>683</v>
@@ -9606,10 +9709,10 @@
         <v>288</v>
       </c>
       <c r="B286" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E286" s="4" t="s">
         <v>468</v>
@@ -9657,10 +9760,10 @@
         <v>291</v>
       </c>
       <c r="B289" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E289" s="4" t="s">
         <v>148</v>
@@ -9674,16 +9777,16 @@
         <v>292</v>
       </c>
       <c r="B290" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D290" t="s">
         <v>584</v>
       </c>
       <c r="E290" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F290" t="s">
         <v>616</v>
@@ -9745,7 +9848,7 @@
         <v>296</v>
       </c>
       <c r="B294" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D294" t="s">
         <v>491</v>
@@ -9793,7 +9896,7 @@
         <v>299</v>
       </c>
       <c r="B297" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>37</v>
@@ -9830,7 +9933,7 @@
         <v>301</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>623</v>
@@ -9850,7 +9953,7 @@
         <v>302</v>
       </c>
       <c r="B300" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C300" s="3">
         <v>3702737055</v>
@@ -9901,7 +10004,7 @@
         <v>305</v>
       </c>
       <c r="B303" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C303" s="3">
         <v>6685097136</v>
@@ -9938,7 +10041,7 @@
         <v>307</v>
       </c>
       <c r="B305" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>627</v>
@@ -9955,7 +10058,7 @@
         <v>308</v>
       </c>
       <c r="B306" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>622</v>
@@ -9975,10 +10078,10 @@
         <v>309</v>
       </c>
       <c r="B307" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E307" s="4" t="s">
         <v>387</v>
@@ -10009,13 +10112,13 @@
         <v>311</v>
       </c>
       <c r="B309" t="s">
+        <v>951</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="D309" t="s">
         <v>952</v>
-      </c>
-      <c r="C309" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="D309" t="s">
-        <v>953</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>585</v>
@@ -10052,7 +10155,7 @@
         <v>5263134860</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F311" t="s">
         <v>616</v>
@@ -10066,7 +10169,7 @@
         <v>404</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E312" s="4" t="s">
         <v>533</v>
@@ -10080,7 +10183,7 @@
         <v>315</v>
       </c>
       <c r="B313" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>627</v>
@@ -10117,10 +10220,10 @@
         <v>317</v>
       </c>
       <c r="B315" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>427</v>
@@ -10154,7 +10257,7 @@
         <v>558</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E317" s="4" t="s">
         <v>559</v>
@@ -10168,7 +10271,7 @@
         <v>320</v>
       </c>
       <c r="B318" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>633</v>
@@ -10239,7 +10342,7 @@
         <v>324</v>
       </c>
       <c r="B322" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>638</v>
@@ -10259,10 +10362,10 @@
         <v>325</v>
       </c>
       <c r="B323" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E323" s="4" t="s">
         <v>577</v>
@@ -10296,7 +10399,7 @@
         <v>327</v>
       </c>
       <c r="B325" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C325" s="3">
         <v>3704007390</v>
@@ -10316,7 +10419,7 @@
         <v>328</v>
       </c>
       <c r="B326" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C326" s="3">
         <v>3703043765</v>
@@ -10376,10 +10479,10 @@
         <v>331</v>
       </c>
       <c r="B329" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E329" s="4" t="s">
         <v>560</v>
@@ -10393,7 +10496,7 @@
         <v>332</v>
       </c>
       <c r="B330" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C330" s="3">
         <v>5248015964</v>
@@ -10410,7 +10513,7 @@
         <v>333</v>
       </c>
       <c r="B331" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C331" s="3">
         <v>5259122245</v>
@@ -10430,10 +10533,10 @@
         <v>334</v>
       </c>
       <c r="B332" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D332" t="s">
         <v>538</v>
@@ -10450,7 +10553,7 @@
         <v>335</v>
       </c>
       <c r="B333" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C333" s="3">
         <v>7708004767</v>
@@ -10484,7 +10587,7 @@
         <v>337</v>
       </c>
       <c r="B335" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C335" s="3">
         <v>7719455708</v>
@@ -10501,10 +10604,10 @@
         <v>338</v>
       </c>
       <c r="B336" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E336" s="4" t="s">
         <v>489</v>
@@ -10569,10 +10672,10 @@
         <v>342</v>
       </c>
       <c r="B340" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E340" s="4" t="s">
         <v>361</v>
@@ -10640,7 +10743,7 @@
         <v>398</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E344" s="4" t="s">
         <v>399</v>
@@ -10654,7 +10757,7 @@
         <v>347</v>
       </c>
       <c r="B345" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C345" s="3">
         <v>5260473015</v>
@@ -10671,7 +10774,7 @@
         <v>348</v>
       </c>
       <c r="B346" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>680</v>
@@ -10691,7 +10794,7 @@
         <v>349</v>
       </c>
       <c r="B347" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>659</v>
@@ -10711,7 +10814,7 @@
         <v>350</v>
       </c>
       <c r="B348" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D348" t="s">
         <v>108</v>
@@ -10745,10 +10848,10 @@
         <v>352</v>
       </c>
       <c r="B350" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D350" t="s">
         <v>477</v>
@@ -10765,16 +10868,16 @@
         <v>354</v>
       </c>
       <c r="B352" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C352" s="3" t="s">
         <v>1131</v>
       </c>
-      <c r="C352" s="3" t="s">
+      <c r="D352" t="s">
         <v>1132</v>
       </c>
-      <c r="D352" t="s">
+      <c r="E352" s="7" t="s">
         <v>1133</v>
-      </c>
-      <c r="E352" s="7" t="s">
-        <v>1134</v>
       </c>
       <c r="F352" t="s">
         <v>662</v>
@@ -10788,7 +10891,7 @@
         <v>83</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E353" s="4" t="s">
         <v>84</v>
@@ -10856,7 +10959,7 @@
         <v>44</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D358" t="s">
         <v>45</v>
@@ -10873,7 +10976,7 @@
         <v>53</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>54</v>
@@ -10887,7 +10990,7 @@
         <v>73</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E360" s="4" t="s">
         <v>74</v>
@@ -10901,7 +11004,7 @@
         <v>80</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E361" s="4" t="s">
         <v>81</v>
@@ -10912,10 +11015,10 @@
         <v>364</v>
       </c>
       <c r="B362" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E362" s="4" t="s">
         <v>82</v>
@@ -10926,10 +11029,10 @@
         <v>365</v>
       </c>
       <c r="B363" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E363" s="4" t="s">
         <v>88</v>
@@ -10940,10 +11043,10 @@
         <v>366</v>
       </c>
       <c r="B364" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E364" s="4" t="s">
         <v>89</v>
@@ -10957,7 +11060,7 @@
         <v>93</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>94</v>
@@ -10971,7 +11074,7 @@
         <v>99</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E366" s="4" t="s">
         <v>100</v>
@@ -10985,7 +11088,7 @@
         <v>103</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E367" s="4" t="s">
         <v>104</v>
@@ -10996,13 +11099,13 @@
         <v>370</v>
       </c>
       <c r="B368" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C368" s="3">
         <v>5263094791</v>
       </c>
       <c r="E368" s="4" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="F368" t="s">
         <v>629</v>
@@ -11013,10 +11116,10 @@
         <v>371</v>
       </c>
       <c r="B369" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E369" s="4" t="s">
         <v>472</v>
@@ -11033,13 +11136,13 @@
         <v>146</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D370" t="s">
         <v>147</v>
       </c>
       <c r="E370" s="7" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="371" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -11064,7 +11167,7 @@
         <v>208</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E372" s="4" t="s">
         <v>209</v>
@@ -11078,7 +11181,7 @@
         <v>219</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E373" s="4" t="s">
         <v>220</v>
@@ -11092,7 +11195,7 @@
         <v>227</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E374" s="7" t="s">
         <v>228</v>
@@ -11131,10 +11234,10 @@
         <v>379</v>
       </c>
       <c r="B377" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E377" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11145,7 +11248,7 @@
         <v>271</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E378" s="7" t="s">
         <v>272</v>
@@ -11156,7 +11259,7 @@
         <v>381</v>
       </c>
       <c r="B379" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C379" s="3">
         <v>5248031148</v>
@@ -11173,7 +11276,7 @@
         <v>289</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E380" s="4" t="s">
         <v>290</v>
@@ -11198,10 +11301,10 @@
         <v>384</v>
       </c>
       <c r="B382" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E382" s="4" t="s">
         <v>519</v>
@@ -11226,7 +11329,7 @@
         <v>386</v>
       </c>
       <c r="B384" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C384" s="3">
         <v>5263093131</v>
@@ -11288,7 +11391,7 @@
         <v>334</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E388" s="4" t="s">
         <v>238</v>
@@ -11302,7 +11405,7 @@
         <v>344</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E389" s="4" t="s">
         <v>345</v>
@@ -11313,10 +11416,10 @@
         <v>392</v>
       </c>
       <c r="B390" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D390" t="s">
         <v>522</v>
@@ -11347,7 +11450,7 @@
         <v>366</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E392" s="4" t="s">
         <v>367</v>
@@ -11358,7 +11461,7 @@
         <v>395</v>
       </c>
       <c r="B393" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C393" s="3" t="s">
         <v>593</v>
@@ -11389,7 +11492,7 @@
         <v>397</v>
       </c>
       <c r="B395" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C395" s="3">
         <v>5257111054</v>
@@ -11431,10 +11534,10 @@
         <v>400</v>
       </c>
       <c r="B398" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E398" s="4" t="s">
         <v>417</v>
@@ -11448,7 +11551,7 @@
         <v>421</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E399" s="4" t="s">
         <v>422</v>
@@ -11462,7 +11565,7 @@
         <v>446</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E400" s="4" t="s">
         <v>447</v>
@@ -11473,7 +11576,7 @@
         <v>403</v>
       </c>
       <c r="B401" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C401" s="3">
         <v>3702092375</v>
@@ -11504,7 +11607,7 @@
         <v>454</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E403" s="4" t="s">
         <v>455</v>
@@ -11515,7 +11618,7 @@
         <v>406</v>
       </c>
       <c r="B404" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C404" s="3">
         <v>2127025472</v>
@@ -11557,13 +11660,13 @@
         <v>409</v>
       </c>
       <c r="B407" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D407" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E407" s="4" t="s">
         <v>542</v>
@@ -11574,7 +11677,7 @@
         <v>410</v>
       </c>
       <c r="B408" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C408" s="3">
         <v>5262145010</v>
@@ -11583,7 +11686,7 @@
         <v>543</v>
       </c>
       <c r="F408" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="409" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -11591,10 +11694,10 @@
         <v>411</v>
       </c>
       <c r="B409" t="s">
+        <v>848</v>
+      </c>
+      <c r="C409" s="3" t="s">
         <v>849</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>850</v>
       </c>
       <c r="E409" s="4" t="s">
         <v>573</v>
@@ -11605,7 +11708,7 @@
         <v>412</v>
       </c>
       <c r="B410" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C410" s="3">
         <v>5256008537</v>
@@ -11633,7 +11736,7 @@
         <v>414</v>
       </c>
       <c r="B412" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>642</v>
@@ -11661,10 +11764,10 @@
         <v>416</v>
       </c>
       <c r="B414" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E414" s="4" t="s">
         <v>580</v>
@@ -11675,16 +11778,16 @@
         <v>417</v>
       </c>
       <c r="B415" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E415" s="7" t="s">
         <v>1162</v>
-      </c>
-      <c r="C415" s="3" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D415" s="4" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E415" s="7" t="s">
-        <v>1163</v>
       </c>
       <c r="F415" t="s">
         <v>631</v>
@@ -11695,16 +11798,16 @@
         <v>418</v>
       </c>
       <c r="B416" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C416" s="3" t="s">
         <v>1164</v>
       </c>
-      <c r="C416" s="3" t="s">
+      <c r="D416" t="s">
         <v>1165</v>
       </c>
-      <c r="D416" t="s">
+      <c r="E416" s="7" t="s">
         <v>1166</v>
-      </c>
-      <c r="E416" s="7" t="s">
-        <v>1167</v>
       </c>
       <c r="F416" t="s">
         <v>658</v>
@@ -11715,16 +11818,16 @@
         <v>419</v>
       </c>
       <c r="B417" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C417" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="C417" s="3" t="s">
+      <c r="D417" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E417" s="7" t="s">
         <v>1169</v>
-      </c>
-      <c r="D417" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E417" s="7" t="s">
-        <v>1170</v>
       </c>
       <c r="F417" t="s">
         <v>658</v>
@@ -11735,16 +11838,16 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C418" s="3" t="s">
         <v>1172</v>
       </c>
-      <c r="C418" s="3" t="s">
+      <c r="D418" t="s">
         <v>1173</v>
       </c>
-      <c r="D418" t="s">
+      <c r="E418" s="4" t="s">
         <v>1174</v>
-      </c>
-      <c r="E418" s="4" t="s">
-        <v>1175</v>
       </c>
       <c r="F418" t="s">
         <v>658</v>
@@ -11755,16 +11858,16 @@
         <v>421</v>
       </c>
       <c r="B419" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C419" s="3" t="s">
         <v>1176</v>
       </c>
-      <c r="C419" s="3" t="s">
+      <c r="D419" t="s">
         <v>1177</v>
       </c>
-      <c r="D419" t="s">
+      <c r="E419" s="7" t="s">
         <v>1178</v>
-      </c>
-      <c r="E419" s="7" t="s">
-        <v>1179</v>
       </c>
       <c r="F419" t="s">
         <v>658</v>
@@ -11775,19 +11878,19 @@
         <v>422</v>
       </c>
       <c r="B420" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D420" t="s">
         <v>1184</v>
       </c>
-      <c r="C420" s="3" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D420" t="s">
+      <c r="E420" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="E420" s="7" t="s">
+      <c r="F420" t="s">
         <v>1186</v>
-      </c>
-      <c r="F420" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -11795,13 +11898,13 @@
         <v>423</v>
       </c>
       <c r="B421" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="E421" s="7" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="F421" t="s">
         <v>658</v>
@@ -11812,16 +11915,16 @@
         <v>424</v>
       </c>
       <c r="B422" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D422" t="s">
         <v>1192</v>
       </c>
-      <c r="C422" s="3" t="s">
+      <c r="E422" s="7" t="s">
         <v>1193</v>
-      </c>
-      <c r="D422" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E422" s="7" t="s">
-        <v>1195</v>
       </c>
       <c r="F422" t="s">
         <v>658</v>
@@ -11832,19 +11935,19 @@
         <v>425</v>
       </c>
       <c r="B423" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D423" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E423" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="C423" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D423" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E423" s="4" t="s">
-        <v>1202</v>
-      </c>
       <c r="F423" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="424" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -11852,19 +11955,19 @@
         <v>426</v>
       </c>
       <c r="B424" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D424" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E424" s="4" t="s">
         <v>1203</v>
       </c>
-      <c r="C424" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D424" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E424" s="4" t="s">
-        <v>1206</v>
-      </c>
       <c r="F424" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -11872,19 +11975,19 @@
         <v>427</v>
       </c>
       <c r="B425" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D425" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E425" s="7" t="s">
         <v>1207</v>
       </c>
-      <c r="C425" s="3" t="s">
-        <v>1208</v>
-      </c>
-      <c r="D425" t="s">
-        <v>1209</v>
-      </c>
-      <c r="E425" s="7" t="s">
-        <v>1210</v>
-      </c>
       <c r="F425" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -11892,16 +11995,16 @@
         <v>428</v>
       </c>
       <c r="B426" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="E426" s="7" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="F426" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -11909,19 +12012,19 @@
         <v>429</v>
       </c>
       <c r="B427" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D427" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E427" s="7" t="s">
         <v>1214</v>
       </c>
-      <c r="C427" s="3" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D427" t="s">
-        <v>1216</v>
-      </c>
-      <c r="E427" s="7" t="s">
-        <v>1217</v>
-      </c>
       <c r="F427" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="428" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -11929,13 +12032,13 @@
         <v>430</v>
       </c>
       <c r="B428" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C428" s="3" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E428" s="7" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F428" t="s">
         <v>658</v>
@@ -11946,39 +12049,39 @@
         <v>431</v>
       </c>
       <c r="B429" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D429" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E429" s="7" t="s">
         <v>1223</v>
       </c>
-      <c r="C429" s="3" t="s">
+      <c r="F429" t="s">
         <v>1224</v>
       </c>
-      <c r="D429" t="s">
-        <v>1225</v>
-      </c>
-      <c r="E429" s="7" t="s">
-        <v>1226</v>
-      </c>
-      <c r="F429" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>432</v>
       </c>
       <c r="B430" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="C430" s="3" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="D430" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="E430" s="7" t="s">
-        <v>1231</v>
+        <v>1364</v>
       </c>
       <c r="F430" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -11986,16 +12089,16 @@
         <v>433</v>
       </c>
       <c r="B431" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="D431" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="E431" s="7" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="F431" t="s">
         <v>658</v>
@@ -12006,16 +12109,16 @@
         <v>434</v>
       </c>
       <c r="B432" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="D432" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="E432" s="4" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="F432" t="s">
         <v>658</v>
@@ -12026,19 +12129,19 @@
         <v>435</v>
       </c>
       <c r="B433" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="D433" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="F433" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="434" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -12046,16 +12149,16 @@
         <v>436</v>
       </c>
       <c r="B434" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="D434" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="E434" s="7" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="F434" t="s">
         <v>654</v>
@@ -12066,16 +12169,16 @@
         <v>437</v>
       </c>
       <c r="B435" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="D435" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="E435" s="7" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="F435" t="s">
         <v>654</v>
@@ -12086,16 +12189,16 @@
         <v>438</v>
       </c>
       <c r="B436" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="C436" s="3" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="D436" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E436" s="4" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="F436" t="s">
         <v>654</v>
@@ -12106,16 +12209,16 @@
         <v>439</v>
       </c>
       <c r="B437" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D437" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="E437" s="7" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="F437" t="s">
         <v>664</v>
@@ -12126,19 +12229,19 @@
         <v>440</v>
       </c>
       <c r="B438" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>605</v>
       </c>
       <c r="D438" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="E438" s="7" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="F438" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12146,19 +12249,19 @@
         <v>441</v>
       </c>
       <c r="B439" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C439" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D439" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E439" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F439" t="s">
         <v>1266</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D439" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E439" s="4" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F439" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12166,16 +12269,16 @@
         <v>442</v>
       </c>
       <c r="B440" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="C440" s="3" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="E440" s="7" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="F440" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12183,19 +12286,19 @@
         <v>443</v>
       </c>
       <c r="B441" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="C441" s="3" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="D441" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="E441" s="7" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="F441" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12203,16 +12306,16 @@
         <v>444</v>
       </c>
       <c r="B442" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="E442" s="7" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="F442" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="443" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -12220,19 +12323,19 @@
         <v>445</v>
       </c>
       <c r="B443" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="C443" s="3" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="D443" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="E443" s="4" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="F443" t="s">
-        <v>1227</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12240,19 +12343,19 @@
         <v>446</v>
       </c>
       <c r="B444" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="C444" s="3" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="D444" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="E444" s="7" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="F444" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="445" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -12260,16 +12363,16 @@
         <v>447</v>
       </c>
       <c r="B445" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="C445" s="3" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="D445" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="E445" s="7" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="F445" t="s">
         <v>654</v>
@@ -12280,19 +12383,19 @@
         <v>448</v>
       </c>
       <c r="B446" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D446" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E446" s="4" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="F446" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="447" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -12300,19 +12403,19 @@
         <v>449</v>
       </c>
       <c r="B447" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C447" s="3" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="D447" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="F447" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12320,16 +12423,16 @@
         <v>450</v>
       </c>
       <c r="B448" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="C448" s="3" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="E448" s="7" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="F448" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12337,16 +12440,16 @@
         <v>451</v>
       </c>
       <c r="B449" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D449" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E449" s="7" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="F449" t="s">
         <v>658</v>
@@ -12357,16 +12460,16 @@
         <v>452</v>
       </c>
       <c r="B450" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C450" s="3" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="D450" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E450" s="4" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="F450" t="s">
         <v>658</v>
@@ -12377,19 +12480,19 @@
         <v>453</v>
       </c>
       <c r="B451" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="D451" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="E451" s="7" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="F451" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="452" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -12397,19 +12500,19 @@
         <v>454</v>
       </c>
       <c r="B452" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E452" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F452" t="s">
         <v>1322</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D452" s="4" t="s">
-        <v>1324</v>
-      </c>
-      <c r="E452" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="F452" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12417,16 +12520,16 @@
         <v>455</v>
       </c>
       <c r="B453" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="D453" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="E453" s="7" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="F453" t="s">
         <v>658</v>
@@ -12437,16 +12540,16 @@
         <v>456</v>
       </c>
       <c r="B454" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C454" s="3" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="D454" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="E454" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="F454" t="s">
         <v>658</v>
@@ -12457,13 +12560,13 @@
         <v>457</v>
       </c>
       <c r="B455" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C455" s="3" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="E455" s="4" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="F455" t="s">
         <v>658</v>
@@ -12474,19 +12577,179 @@
         <v>458</v>
       </c>
       <c r="B456" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="D456" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="E456" s="7" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="F456" t="s">
         <v>658</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>459</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E457" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F457" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>460</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E458" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F458" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>461</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E459" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F459" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>462</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E460" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F460" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>463</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E461" s="7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F461" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>464</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E462" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F462" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>465</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E463" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F463" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>466</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D464" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E464" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F464" t="s">
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -12592,7 +12855,7 @@
     <hyperlink ref="E427" r:id="rId95" xr:uid="{1546BBEB-EDC6-490F-9A21-35FEB3F958DF}"/>
     <hyperlink ref="E428" r:id="rId96" xr:uid="{CC99FCFB-AB64-4252-9653-2266DAB66A67}"/>
     <hyperlink ref="E429" r:id="rId97" xr:uid="{09BC035C-ADB7-40C8-8712-DCAFD19E653F}"/>
-    <hyperlink ref="E430" r:id="rId98" xr:uid="{3B6AB036-6134-4F3E-8D34-52850F0CCED2}"/>
+    <hyperlink ref="E430" r:id="rId98" display="garant@garant1.ru" xr:uid="{3B6AB036-6134-4F3E-8D34-52850F0CCED2}"/>
     <hyperlink ref="E431" r:id="rId99" xr:uid="{20A51DD5-8AB1-4969-B51C-714C8BC13FF2}"/>
     <hyperlink ref="E433" r:id="rId100" xr:uid="{49FF83F9-F9E7-4597-A901-C9A00125A959}"/>
     <hyperlink ref="E67" r:id="rId101" xr:uid="{4FA33187-FDDD-4856-BAD8-5BAEBD00DAAD}"/>
@@ -12621,8 +12884,15 @@
     <hyperlink ref="E453" r:id="rId124" xr:uid="{A48427DC-A126-4D1B-B254-84140898C8CE}"/>
     <hyperlink ref="E454" r:id="rId125" xr:uid="{0DD8B6C2-385C-4DD9-B37D-7AB7B4E1B124}"/>
     <hyperlink ref="E456" r:id="rId126" xr:uid="{6B8029D8-DE51-4569-A1FC-B63F1B64549D}"/>
+    <hyperlink ref="E457" r:id="rId127" xr:uid="{0BD23134-63EE-4FF9-B88E-6050003CE92F}"/>
+    <hyperlink ref="E458" r:id="rId128" xr:uid="{A8A202A3-DC04-4C86-AF2D-CA40A1105066}"/>
+    <hyperlink ref="E459" r:id="rId129" xr:uid="{A9552973-AE55-472D-9DA8-E3C0D242AC92}"/>
+    <hyperlink ref="E460" r:id="rId130" xr:uid="{717E6015-0BAB-469D-A641-91D546F50A0D}"/>
+    <hyperlink ref="E461" r:id="rId131" xr:uid="{A7D82F65-2976-41F2-993E-C9B71AF5CEBF}"/>
+    <hyperlink ref="E463" r:id="rId132" xr:uid="{B9BB0974-638B-40E4-873B-FE60BEBA07A0}"/>
+    <hyperlink ref="E464" r:id="rId133" xr:uid="{7E2215E1-AF36-42D3-992B-900739C846A9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId127"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId134"/>
 </worksheet>
 </file>